--- a/study_chart.xlsx
+++ b/study_chart.xlsx
@@ -1,22 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="15120" windowHeight="8010"/>
+    <workbookView windowWidth="24000" windowHeight="10530"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Июнь" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -24,16 +37,46 @@
     <t>№</t>
   </si>
   <si>
+    <t>День недели</t>
+  </si>
+  <si>
     <t>Дата</t>
   </si>
   <si>
-    <t>День недели</t>
-  </si>
-  <si>
-    <t>С</t>
-  </si>
-  <si>
-    <t>Frame25</t>
+    <t>Медитация</t>
+  </si>
+  <si>
+    <t>Сметы</t>
+  </si>
+  <si>
+    <t>Стройка</t>
+  </si>
+  <si>
+    <t>Codewars</t>
+  </si>
+  <si>
+    <t>Трекер задач</t>
+  </si>
+  <si>
+    <t>Fram 25</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Сб</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>Вс</t>
+  </si>
+  <si>
+    <t>Пн</t>
+  </si>
+  <si>
+    <t>Вт</t>
   </si>
   <si>
     <t>Ср</t>
@@ -43,58 +86,200 @@
   </si>
   <si>
     <t>Пт</t>
-  </si>
-  <si>
-    <t>Сб</t>
-  </si>
-  <si>
-    <t>Вс</t>
-  </si>
-  <si>
-    <t>Пн</t>
-  </si>
-  <si>
-    <t>Вт</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="dd\.mmm"/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1C1917"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1C1917"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color rgb="FF1C1917"/>
       <name val="Impact"/>
-      <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1C1917"/>
+      <name val="Courier New"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1C1917"/>
+      <name val="Courier New"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -109,18 +294,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE6A817"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF4EFEA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6A817"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -132,9 +503,7 @@
       <left style="thin">
         <color rgb="FF4A3B32"/>
       </left>
-      <right style="thin">
-        <color rgb="FF4A3B32"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="FF4A3B32"/>
       </top>
@@ -147,7 +516,9 @@
       <left style="thin">
         <color rgb="FF4A3B32"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color rgb="FF4A3B32"/>
+      </right>
       <top style="thin">
         <color rgb="FF4A3B32"/>
       </top>
@@ -180,50 +551,356 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FF1C1917"/>
-      <color rgb="FFE6A817"/>
-      <color rgb="FFC1292E"/>
-      <color rgb="FF1B4965"/>
-      <color rgb="FF4A3B32"/>
-      <color rgb="FFF4EFEA"/>
-      <color rgb="FF3A2E2A"/>
+      <color rgb="001C1917"/>
+      <color rgb="00E6A817"/>
+      <color rgb="00C1292E"/>
+      <color rgb="001B4965"/>
+      <color rgb="004A3B32"/>
+      <color rgb="00F4EFEA"/>
+      <color rgb="003A2E2A"/>
     </mruColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -506,361 +1183,316 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="H9:L32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="H9:Q21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="7" width="9.140625" style="1"/>
+    <col min="1" max="7" width="9.14159292035398" style="1"/>
     <col min="8" max="8" width="5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="1"/>
-    <col min="12" max="12" width="10" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="11.283185840708" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.283185840708" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.4867256637168" style="1" customWidth="1"/>
+    <col min="12" max="13" width="11.353982300885" style="1" customWidth="1"/>
+    <col min="14" max="14" width="10" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7610619469027" style="1" customWidth="1"/>
+    <col min="16" max="17" width="10" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.14159292035398" style="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="8:12" ht="45" customHeight="1">
-      <c r="H9" s="7" t="s">
+    <row r="9" ht="45" customHeight="1" spans="8:17">
+      <c r="H9" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="9"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="10"/>
     </row>
-    <row r="10" spans="8:12" ht="30" customHeight="1">
-      <c r="H10" s="4" t="s">
+    <row r="10" ht="30" customHeight="1" spans="8:17">
+      <c r="H10" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="K10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="8:17">
+      <c r="H11" s="4">
+        <v>1</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="8">
+        <v>46193</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+    </row>
+    <row r="12" spans="8:17">
+      <c r="H12" s="4">
         <v>2</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="I12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="8">
+        <v>46194</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+    </row>
+    <row r="13" spans="8:17">
+      <c r="H13" s="4">
+        <v>3</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="8">
+        <v>46195</v>
+      </c>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+    </row>
+    <row r="14" spans="8:17">
+      <c r="H14" s="4">
         <v>4</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="I14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="8">
+        <v>46196</v>
+      </c>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+    </row>
+    <row r="15" spans="8:17">
+      <c r="H15" s="4">
         <v>5</v>
       </c>
+      <c r="I15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="8">
+        <v>46197</v>
+      </c>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
     </row>
-    <row r="11" spans="8:12">
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
-      <c r="I11" s="3" t="s">
+    <row r="16" spans="8:17">
+      <c r="H16" s="4">
         <v>6</v>
       </c>
-      <c r="J11" s="6">
-        <v>46141</v>
-      </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+      <c r="I16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="8">
+        <v>46198</v>
+      </c>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
     </row>
-    <row r="12" spans="8:12">
-      <c r="H12" s="2">
-        <v>2</v>
-      </c>
-      <c r="I12" s="3" t="s">
+    <row r="17" spans="8:17">
+      <c r="H17" s="4">
         <v>7</v>
       </c>
-      <c r="J12" s="6">
-        <v>46142</v>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="I17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="8">
+        <v>46199</v>
+      </c>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
     </row>
-    <row r="13" spans="8:12">
-      <c r="H13" s="2">
-        <v>3</v>
-      </c>
-      <c r="I13" s="3" t="s">
+    <row r="18" spans="8:17">
+      <c r="H18" s="4">
         <v>8</v>
       </c>
-      <c r="J13" s="6">
-        <v>46143</v>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
+      <c r="I18" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J18" s="8">
+        <v>46200</v>
+      </c>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
     </row>
-    <row r="14" spans="8:12">
-      <c r="H14" s="2">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3" t="s">
+    <row r="19" spans="8:17">
+      <c r="H19" s="4">
         <v>9</v>
       </c>
-      <c r="J14" s="6">
-        <v>46144</v>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
+      <c r="I19" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="8">
+        <v>46201</v>
+      </c>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
     </row>
-    <row r="15" spans="8:12">
-      <c r="H15" s="2">
-        <v>5</v>
-      </c>
-      <c r="I15" s="3" t="s">
+    <row r="20" spans="8:17">
+      <c r="H20" s="4">
         <v>10</v>
       </c>
-      <c r="J15" s="6">
-        <v>46145</v>
-      </c>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
+      <c r="I20" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="8">
+        <v>46202</v>
+      </c>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
     </row>
-    <row r="16" spans="8:12">
-      <c r="H16" s="2">
-        <v>6</v>
-      </c>
-      <c r="I16" s="3" t="s">
+    <row r="21" spans="8:17">
+      <c r="H21" s="4">
         <v>11</v>
       </c>
-      <c r="J16" s="6">
-        <v>46146</v>
-      </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-    </row>
-    <row r="17" spans="8:12">
-      <c r="H17" s="2">
-        <v>7</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J17" s="6">
-        <v>46147</v>
-      </c>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-    </row>
-    <row r="18" spans="8:12">
-      <c r="H18" s="2">
-        <v>8</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J18" s="6">
-        <v>46148</v>
-      </c>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-    </row>
-    <row r="19" spans="8:12">
-      <c r="H19" s="2">
-        <v>9</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J19" s="6">
-        <v>46149</v>
-      </c>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" spans="8:12">
-      <c r="H20" s="2">
-        <v>10</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="6">
-        <v>46150</v>
-      </c>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="21" spans="8:12">
-      <c r="H21" s="2">
-        <v>11</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J21" s="6">
-        <v>46151</v>
-      </c>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-    </row>
-    <row r="22" spans="8:12">
-      <c r="H22" s="2">
-        <v>12</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J22" s="6">
-        <v>46152</v>
-      </c>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-    </row>
-    <row r="23" spans="8:12">
-      <c r="H23" s="2">
-        <v>13</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J23" s="6">
-        <v>46153</v>
-      </c>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-    </row>
-    <row r="24" spans="8:12">
-      <c r="H24" s="2">
-        <v>14</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J24" s="6">
-        <v>46154</v>
-      </c>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-    </row>
-    <row r="25" spans="8:12">
-      <c r="H25" s="2">
+      <c r="I21" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J25" s="6">
-        <v>46155</v>
-      </c>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-    </row>
-    <row r="26" spans="8:12">
-      <c r="H26" s="2">
-        <v>16</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J26" s="6">
-        <v>46156</v>
-      </c>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-    </row>
-    <row r="27" spans="8:12">
-      <c r="H27" s="2">
-        <v>17</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J27" s="6">
-        <v>46157</v>
-      </c>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-    </row>
-    <row r="28" spans="8:12">
-      <c r="H28" s="2">
-        <v>18</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J28" s="6">
-        <v>46158</v>
-      </c>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-    </row>
-    <row r="29" spans="8:12">
-      <c r="H29" s="2">
-        <v>19</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J29" s="6">
-        <v>46159</v>
-      </c>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-    </row>
-    <row r="30" spans="8:12">
-      <c r="H30" s="2">
-        <v>20</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="J30" s="6">
-        <v>46160</v>
-      </c>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-    </row>
-    <row r="31" spans="8:12">
-      <c r="H31" s="2">
-        <v>21</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J31" s="6">
-        <v>46161</v>
-      </c>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-    </row>
-    <row r="32" spans="8:12">
-      <c r="H32" s="2">
-        <v>22</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J32" s="6">
-        <v>46162</v>
-      </c>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
+      <c r="J21" s="8">
+        <v>46203</v>
+      </c>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="H9:L9"/>
+    <mergeCell ref="H9:Q9"/>
   </mergeCells>
+  <conditionalFormatting sqref="K11:Q21">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>Q11="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
+  <headerFooter/>
 </worksheet>
 </file>